--- a/pedidos.xlsx
+++ b/pedidos.xlsx
@@ -1,45 +1,193 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CristobalTreknaisRoj\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4938B4A5-4260-466E-8F6F-50F515CF16CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Pedidos" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Pedidos" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+  <si>
+    <t>oc</t>
+  </si>
+  <si>
+    <t>producto</t>
+  </si>
+  <si>
+    <t>obra</t>
+  </si>
+  <si>
+    <t>proveedor</t>
+  </si>
+  <si>
+    <t>etapa</t>
+  </si>
+  <si>
+    <t>eta</t>
+  </si>
+  <si>
+    <t>detalle</t>
+  </si>
+  <si>
+    <t>Antena Starlink Gen3</t>
+  </si>
+  <si>
+    <t>Fortinet FG-100F + licencia</t>
+  </si>
+  <si>
+    <t>Cables y conectores red</t>
+  </si>
+  <si>
+    <t>Switch 48 puertos PoE</t>
+  </si>
+  <si>
+    <t>FINNING CHILE S.A.</t>
+  </si>
+  <si>
+    <t>REPUESTO</t>
+  </si>
+  <si>
+    <t>retiro con Camión , se informa hace dos semanas atrás a jefatura</t>
+  </si>
+  <si>
+    <t>se retira con camion</t>
+  </si>
+  <si>
+    <t>no disponible para retiro</t>
+  </si>
+  <si>
+    <t>no está para retiro , atendida por Israel campillay</t>
+  </si>
+  <si>
+    <t>42 tuercas pendientes</t>
+  </si>
+  <si>
+    <t>no lista para retirp</t>
+  </si>
+  <si>
+    <t>con reparto a la negra</t>
+  </si>
+  <si>
+    <t>no está para retiro</t>
+  </si>
+  <si>
+    <t>sin orden de compra , se avisa a Michelle con retiro para el 10/02</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>S/N</t>
+  </si>
+  <si>
+    <t>GUIDO ALAN VALENZUELA GOMEZ</t>
+  </si>
+  <si>
+    <t>GYG THOMAS SAFETY S.A.</t>
+  </si>
+  <si>
+    <t>MAX SERVICE SEGURIDAD INDUSTRIAL SPA</t>
+  </si>
+  <si>
+    <t>OC342245</t>
+  </si>
+  <si>
+    <t>OC342507</t>
+  </si>
+  <si>
+    <t>OC343170</t>
+  </si>
+  <si>
+    <t>OC343298</t>
+  </si>
+  <si>
+    <t>OC344233</t>
+  </si>
+  <si>
+    <t>OC344265</t>
+  </si>
+  <si>
+    <t>OC344266</t>
+  </si>
+  <si>
+    <t>OC344379</t>
+  </si>
+  <si>
+    <t>OC344632</t>
+  </si>
+  <si>
+    <t>OC344647</t>
+  </si>
+  <si>
+    <t>OC341127</t>
+  </si>
+  <si>
+    <t>ZALDIVAR II</t>
+  </si>
+  <si>
+    <t>No Entregada</t>
+  </si>
+  <si>
+    <t>Entrega Parcial</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00E8621A"/>
+        <fgColor rgb="FFE8621A"/>
       </patternFill>
     </fill>
   </fills>
@@ -55,84 +203,26 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="3">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -420,211 +510,321 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G5"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="28" customWidth="1" min="2" max="2"/>
-    <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="45" customWidth="1" min="7" max="7"/>
+    <col min="1" max="1" width="16" customWidth="1"/>
+    <col min="2" max="2" width="28" customWidth="1"/>
+    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="4" max="4" width="36.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="45" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>oc</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>producto</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>obra</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>proveedor</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>etapa</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>eta</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>detalle</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>OC-2026-014</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Antena Starlink Gen3</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>El Abra</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Starlink Chile</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>En tránsito</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Despacho confirmado por courier, llega a bodega central antes de subir a faena</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>OC-2026-015</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Fortinet FG-100F + licencia</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Faena Sur</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Fortinet Distribuidor</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>Despachada</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2026-06-30</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Pendiente factura para retiro en bodega proveedor</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>OC-2026-016</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Cables y conectores red</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>El Abra</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Proveedor Local SpA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>OC</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>2026-07-02</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>OC enviada, esperando aprobación de gerencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>OC-2026-017</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Switch 48 puertos PoE</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Lo Pinto</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Cisco Chile</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>Llegó a obra</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>2026-06-10</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>En bodega obra, pendiente revisión TI para recepción conforme</t>
-        </is>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>38</v>
+      </c>
+      <c r="D2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2">
+        <v>46059</v>
+      </c>
+      <c r="G2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" t="s">
+        <v>39</v>
+      </c>
+      <c r="F3" s="2">
+        <v>46031</v>
+      </c>
+      <c r="G3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" t="s">
+        <v>38</v>
+      </c>
+      <c r="D4" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" s="2">
+        <v>46049</v>
+      </c>
+      <c r="G4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" s="2">
+        <v>46050</v>
+      </c>
+      <c r="G5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" t="s">
+        <v>38</v>
+      </c>
+      <c r="D6" t="s">
+        <v>24</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="2">
+        <v>46051</v>
+      </c>
+      <c r="G6" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>32</v>
+      </c>
+      <c r="B7" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" t="s">
+        <v>38</v>
+      </c>
+      <c r="D7" t="s">
+        <v>11</v>
+      </c>
+      <c r="E7" t="s">
+        <v>39</v>
+      </c>
+      <c r="F7" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G7" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C8" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" t="s">
+        <v>40</v>
+      </c>
+      <c r="F8" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" t="s">
+        <v>12</v>
+      </c>
+      <c r="C9" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" t="s">
+        <v>25</v>
+      </c>
+      <c r="E9" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="2">
+        <v>46058</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" t="s">
+        <v>35</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" t="s">
+        <v>38</v>
+      </c>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" s="2">
+        <v>46057</v>
+      </c>
+      <c r="G10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D11" t="s">
+        <v>26</v>
+      </c>
+      <c r="E11" t="s">
+        <v>39</v>
+      </c>
+      <c r="F11" s="2">
+        <v>46062</v>
+      </c>
+      <c r="G11" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" t="s">
+        <v>38</v>
+      </c>
+      <c r="D12" t="s">
+        <v>11</v>
+      </c>
+      <c r="E12" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="2">
+        <v>46062</v>
+      </c>
+      <c r="G12" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B13" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" t="s">
+        <v>38</v>
+      </c>
+      <c r="D13" t="s">
+        <v>11</v>
+      </c>
+      <c r="E13" t="s">
+        <v>39</v>
+      </c>
+      <c r="F13" s="2">
+        <v>46042</v>
+      </c>
+      <c r="G13" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="E2:E1000" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="0" type="list">
+    <dataValidation type="list" sqref="E2:E1000" xr:uid="{00000000-0002-0000-0000-000000000000}">
       <formula1>"OC,Aprobada,Despachada,En tránsito,Llegó a obra,Recepción conforme"</formula1>
     </dataValidation>
   </dataValidations>

--- a/pedidos.xlsx
+++ b/pedidos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\CristobalTreknaisRoj\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4938B4A5-4260-466E-8F6F-50F515CF16CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B308B4F4-84CE-4C2B-9D5B-1B3EC6C45574}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="44">
   <si>
     <t>oc</t>
   </si>
@@ -152,10 +152,19 @@
     <t>ZALDIVAR II</t>
   </si>
   <si>
-    <t>No Entregada</t>
-  </si>
-  <si>
-    <t>Entrega Parcial</t>
+    <t>Aprobada</t>
+  </si>
+  <si>
+    <t>En tránsito</t>
+  </si>
+  <si>
+    <t>Llegó a obra</t>
+  </si>
+  <si>
+    <t>Recepción conforme</t>
+  </si>
+  <si>
+    <t>Despachada</t>
   </si>
 </sst>
 </file>
@@ -606,7 +615,7 @@
         <v>11</v>
       </c>
       <c r="E4" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F4" s="2">
         <v>46049</v>
@@ -629,7 +638,7 @@
         <v>11</v>
       </c>
       <c r="E5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F5" s="2">
         <v>46050</v>
@@ -652,7 +661,7 @@
         <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F6" s="2">
         <v>46051</v>
@@ -675,7 +684,7 @@
         <v>11</v>
       </c>
       <c r="E7" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="F7" s="2">
         <v>46058</v>
@@ -721,7 +730,7 @@
         <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F9" s="2">
         <v>46058</v>
@@ -744,7 +753,7 @@
         <v>11</v>
       </c>
       <c r="E10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="F10" s="2">
         <v>46057</v>
@@ -767,7 +776,7 @@
         <v>26</v>
       </c>
       <c r="E11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" s="2">
         <v>46062</v>
@@ -790,7 +799,7 @@
         <v>11</v>
       </c>
       <c r="E12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2">
         <v>46062</v>
